--- a/hrcheck/examples/本月花名册_问题报告.xlsx
+++ b/hrcheck/examples/本月花名册_问题报告.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,6 +714,135 @@
         <v>1</v>
       </c>
       <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <f>==== 数据概览 =====</f>
+        <v/>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>总记录数</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>55</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>工号 非空</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>55</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>姓名 非空</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>54</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>部门 非空</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>54</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>岗位 非空</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>54</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>入职日期 非空</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>55</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>用工类型 非空</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>55</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>直属上级工号 非空</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>41</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>74.5%</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
